--- a/jira_export_2026-10-05.xlsx
+++ b/jira_export_2026-10-05.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>50 h</t>
+          <t>60 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P122"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1342,12 +1342,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35666</t>
+          <t>PDMDEP-35696</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BRISSAC LOIRE AUBANCE] - 1/2 journée d'accompagnement a GEODP Placier </t>
+          <t xml:space="preserve">[COMMUNE DE HARFLEUR] - Migration Placier </t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
+          <t>COMMUNE DE HARFLEUR</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/2 journée d'accompagnement a GEODP Placier </t>
+          <t xml:space="preserve">Migration Placier </t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -1389,22 +1389,14 @@
         <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35672</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>00181382</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr"/>
+      <c r="M9" s="11" t="inlineStr"/>
       <c r="N9" s="12" t="n">
-        <v>427.5</v>
-      </c>
-      <c r="O9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -1414,32 +1406,32 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35646</t>
+          <t>PDMDEP-35666</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
+          <t xml:space="preserve">[COMMUNE DE BRISSAC LOIRE AUBANCE] - 1/2 journée d'accompagnement a GEODP Placier </t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GEX</t>
+          <t>COMMUNE DE BRISSAC LOIRE AUBANCE</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
+          <t xml:space="preserve">1/2 journée d'accompagnement a GEODP Placier </t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -1449,32 +1441,32 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="J10" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35652</t>
+          <t>PDMDEP-35672</t>
         </is>
       </c>
       <c r="M10" s="15" t="inlineStr">
         <is>
-          <t>00181167</t>
+          <t>00181382</t>
         </is>
       </c>
       <c r="N10" s="16" t="n">
-        <v>3000</v>
+        <v>427.5</v>
       </c>
       <c r="O10" s="13" t="n">
         <v>0</v>
@@ -1486,32 +1478,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35627</t>
+          <t>PDMDEP-35646</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t xml:space="preserve">[VILLE DE GEX] - Client Standard - Migration vers Lit Expert </t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANNEMASSE</t>
+          <t>VILLE DE GEX</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
+          <t xml:space="preserve">Client Standard - Passsage sur expert </t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1521,7 +1513,7 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
@@ -1537,16 +1529,16 @@
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35636</t>
+          <t>PDMDEP-35652</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00181182</t>
+          <t>00181167</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1852.8</v>
+        <v>3000</v>
       </c>
       <c r="O11" s="13" t="n">
         <v>0</v>
@@ -1558,32 +1550,32 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35627</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t>[COMMUNE D'ANNEMASSE] - Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>COMMUNE D'ANNEMASSE</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier) + Acquisition modules Voirie et Terrasses</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -1593,32 +1585,32 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J12" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35636</t>
         </is>
       </c>
       <c r="M12" s="15" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181182</t>
         </is>
       </c>
       <c r="N12" s="16" t="n">
-        <v>805.5</v>
+        <v>1852.8</v>
       </c>
       <c r="O12" s="13" t="n">
         <v>0</v>
@@ -1630,32 +1622,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1665,32 +1657,32 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>4399.5</v>
+        <v>805.5</v>
       </c>
       <c r="O13" s="13" t="n">
         <v>0</v>
@@ -1702,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfert de compétence Analyse </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1737,7 +1729,7 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
@@ -1753,16 +1745,16 @@
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>455</v>
+        <v>4399.5</v>
       </c>
       <c r="O14" s="13" t="n">
         <v>0</v>
@@ -1774,12 +1766,12 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35445</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1789,12 +1781,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOURG EN BRESSE</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1804,7 +1796,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1814,21 +1806,29 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12" t="n">
+        <v>455</v>
+      </c>
+      <c r="O15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1838,27 +1838,27 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35445</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE BOURG EN BRESSE</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -1885,22 +1885,14 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr"/>
+      <c r="M16" s="15" t="inlineStr"/>
       <c r="N16" s="16" t="n">
-        <v>1470.38</v>
-      </c>
-      <c r="O16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="16" t="n">
@@ -1910,32 +1902,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>GeODP - Migration V2 (presta)</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1945,12 +1937,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
@@ -1961,16 +1953,16 @@
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>5783.002</v>
+        <v>1470.38</v>
       </c>
       <c r="O17" s="13" t="n">
         <v>0</v>
@@ -1982,27 +1974,27 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35313</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
+          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAREOULT</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Migration Geodp Placier</t>
+          <t>GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -2022,27 +2014,27 @@
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35319</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00179389</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>1053</v>
+        <v>5783.002</v>
       </c>
       <c r="O18" s="13" t="n">
         <v>0</v>
@@ -2054,27 +2046,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2089,12 +2081,12 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
@@ -2105,16 +2097,16 @@
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>250.5</v>
+        <v>1053</v>
       </c>
       <c r="O19" s="13" t="n">
         <v>0</v>
@@ -2126,12 +2118,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35261</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2141,12 +2133,12 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>Reprise des données TLPE</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -2166,29 +2158,21 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35139</t>
-        </is>
-      </c>
-      <c r="M20" s="15" t="inlineStr">
-        <is>
-          <t>00178821</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L20" s="15" t="inlineStr"/>
+      <c r="M20" s="15" t="inlineStr"/>
       <c r="N20" s="16" t="n">
-        <v>1465.2</v>
-      </c>
-      <c r="O20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="16" t="n">
@@ -2198,12 +2182,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2213,12 +2197,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2233,12 +2217,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2249,16 +2233,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>394</v>
+        <v>250.5</v>
       </c>
       <c r="O21" s="13" t="n">
         <v>0</v>
@@ -2270,32 +2254,32 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -2305,12 +2289,12 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -2321,16 +2305,16 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>1100</v>
+        <v>1465.2</v>
       </c>
       <c r="O22" s="13" t="n">
         <v>0</v>
@@ -2342,32 +2326,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2377,12 +2361,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2393,16 +2377,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>960</v>
+        <v>394</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>0</v>
@@ -2414,32 +2398,32 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2449,32 +2433,32 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>1073.25</v>
+        <v>1100</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
@@ -2486,27 +2470,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2526,27 +2510,27 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>243.6</v>
+        <v>960</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2558,12 +2542,12 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2573,12 +2557,12 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -2593,12 +2577,12 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
@@ -2609,16 +2593,16 @@
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>2763.25</v>
+        <v>1073.25</v>
       </c>
       <c r="O26" s="13" t="n">
         <v>0</v>
@@ -2630,32 +2614,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2665,49 +2649,49 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="12" t="n">
-        <v>516</v>
+        <v>243.6</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2717,12 +2701,12 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -2753,16 +2737,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>1400</v>
+        <v>2763.25</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2774,32 +2758,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2809,49 +2793,49 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0.75</v>
+        <v>4</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>0</v>
+        <v>516</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2861,12 +2845,12 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
@@ -2881,32 +2865,32 @@
       </c>
       <c r="H30" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J30" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>1620</v>
+        <v>1400</v>
       </c>
       <c r="O30" s="13" t="n">
         <v>0</v>
@@ -2918,32 +2902,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2953,34 +2937,34 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>936</v>
-      </c>
-      <c r="O31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2990,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -3025,32 +3009,32 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J32" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>344</v>
+        <v>1620</v>
       </c>
       <c r="O32" s="13" t="n">
         <v>0</v>
@@ -3062,27 +3046,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3102,27 +3086,27 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>153.9</v>
+        <v>936</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3134,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3169,32 +3153,32 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>4150</v>
+        <v>344</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3206,27 +3190,27 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3246,7 +3230,7 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
@@ -3257,16 +3241,16 @@
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2500</v>
+        <v>153.9</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3278,32 +3262,32 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -3313,12 +3297,12 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J36" s="15" t="n">
@@ -3329,16 +3313,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>2649.6</v>
+        <v>4150</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3350,27 +3334,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3390,7 +3374,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3401,16 +3385,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>175</v>
+        <v>2500</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3422,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3457,12 +3441,12 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3473,16 +3457,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>775.6</v>
+        <v>2649.6</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3494,27 +3478,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,7 +3518,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3529,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>5388.936</v>
+        <v>175</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3566,27 +3550,27 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3601,12 +3585,12 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -3617,16 +3601,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>177.5</v>
+        <v>775.6</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3638,12 +3622,12 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3653,12 +3637,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3673,12 +3657,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3689,16 +3673,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1700</v>
+        <v>5388.936</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3710,12 +3694,12 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -3725,12 +3709,12 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3750,7 +3734,7 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -3761,16 +3745,16 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>2696</v>
+        <v>177.5</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3782,27 +3766,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3817,12 +3801,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3833,16 +3817,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>170</v>
+        <v>1700</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3854,32 +3838,32 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
@@ -3889,32 +3873,32 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>3000</v>
+        <v>2696</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3926,32 +3910,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3961,32 +3945,32 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1980</v>
+        <v>170</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>0</v>
@@ -3998,32 +3982,32 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4033,32 +4017,32 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="O46" s="13" t="n">
         <v>0</v>
@@ -4070,32 +4054,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4105,32 +4089,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>170</v>
+        <v>1980</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4142,32 +4126,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4177,32 +4161,32 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>186.235</v>
+        <v>700</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4214,32 +4198,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4249,12 +4233,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4265,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1890</v>
+        <v>170</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4286,27 +4270,27 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
@@ -4326,27 +4310,27 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>400</v>
+        <v>186.235</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4358,27 +4342,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4398,27 +4382,27 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>552</v>
+        <v>1890</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4430,32 +4414,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4470,27 +4454,27 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>203.5</v>
+        <v>400</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4502,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4537,32 +4521,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2000</v>
+        <v>552</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4574,12 +4558,12 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -4589,12 +4573,12 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4609,28 +4593,28 @@
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K54" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
@@ -4646,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4681,12 +4665,12 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
@@ -4697,16 +4681,16 @@
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>171.4</v>
+        <v>2000</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4718,32 +4702,32 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -4753,12 +4737,12 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
@@ -4769,16 +4753,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>400</v>
+        <v>203.5</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
@@ -4790,32 +4774,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4825,12 +4809,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4841,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>6177.52</v>
+        <v>171.4</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4862,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -4902,7 +4886,7 @@
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J58" s="15" t="n">
@@ -4913,16 +4897,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4934,61 +4918,69 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr"/>
-      <c r="M59" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33440</t>
+        </is>
+      </c>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>00166923</t>
+        </is>
+      </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
+        <v>6177.52</v>
+      </c>
+      <c r="O59" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4998,27 +4990,27 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5038,7 +5030,7 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5049,16 +5041,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5070,69 +5062,61 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33245</t>
-        </is>
-      </c>
-      <c r="M61" s="11" t="inlineStr">
-        <is>
-          <t>00166748</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr"/>
       <c r="N61" s="12" t="n">
-        <v>149</v>
-      </c>
-      <c r="O61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5142,32 +5126,32 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5182,7 +5166,7 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
@@ -5193,16 +5177,16 @@
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>337.5</v>
+        <v>240</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>0</v>
@@ -5214,32 +5198,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5249,12 +5233,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5265,16 +5249,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5286,32 +5270,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5321,12 +5305,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5337,16 +5321,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>1047</v>
+        <v>337.5</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5358,12 +5342,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5373,12 +5357,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5398,27 +5382,27 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5430,27 +5414,27 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -5470,27 +5454,27 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>200</v>
+        <v>1047</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5502,32 +5486,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5537,12 +5521,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5553,16 +5537,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>680.8</v>
+        <v>400</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5574,12 +5558,12 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5589,12 +5573,12 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
@@ -5614,7 +5598,7 @@
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
@@ -5625,16 +5609,16 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>2614.5</v>
+        <v>200</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5646,32 +5630,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5681,12 +5665,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5697,16 +5681,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>403.074</v>
+        <v>680.8</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5718,12 +5702,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5733,12 +5717,12 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5753,12 +5737,12 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5769,16 +5753,16 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>276</v>
+        <v>2614.5</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5790,12 +5774,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5805,12 +5789,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5830,7 +5814,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5841,16 +5825,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>142.1</v>
+        <v>403.074</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5862,27 +5846,27 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -5897,32 +5881,32 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>11278.05</v>
+        <v>276</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5934,12 +5918,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5949,12 +5933,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5974,27 +5958,27 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1000</v>
+        <v>142.1</v>
       </c>
       <c r="O73" s="13" t="n">
         <v>0</v>
@@ -6006,27 +5990,27 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
@@ -6046,7 +6030,7 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
@@ -6057,16 +6041,16 @@
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>220</v>
+        <v>11278.05</v>
       </c>
       <c r="O74" s="13" t="n">
         <v>0</v>
@@ -6078,32 +6062,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6113,12 +6097,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6129,16 +6113,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
@@ -6150,32 +6134,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6185,32 +6169,32 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>910</v>
+        <v>220</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6222,27 +6206,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6262,7 +6246,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6273,16 +6257,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>3240</v>
+        <v>450</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6294,32 +6278,32 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6329,32 +6313,32 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>1050</v>
+        <v>910</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6366,27 +6350,27 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6406,7 +6390,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6417,16 +6401,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>433.5</v>
+        <v>3240</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6438,32 +6422,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6473,34 +6457,34 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="16" t="n">
+        <v>1050</v>
+      </c>
+      <c r="O80" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
@@ -6510,12 +6494,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6525,12 +6509,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6545,12 +6529,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6561,16 +6545,16 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>285</v>
+        <v>433.5</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6582,12 +6566,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6597,12 +6581,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6617,34 +6601,34 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="O82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
@@ -6654,12 +6638,12 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6669,12 +6653,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6689,12 +6673,12 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
@@ -6705,16 +6689,16 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="O83" s="13" t="n">
         <v>0</v>
@@ -6726,32 +6710,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6761,32 +6745,32 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
@@ -6798,32 +6782,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6833,32 +6817,32 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K85" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1088.5</v>
+        <v>210</v>
       </c>
       <c r="O85" s="13" t="n">
         <v>0</v>
@@ -6870,27 +6854,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6905,12 +6889,12 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6921,16 +6905,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>130</v>
+        <v>203.5</v>
       </c>
       <c r="O86" s="13" t="n">
         <v>0</v>
@@ -6942,32 +6926,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6977,12 +6961,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6993,16 +6977,16 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>210</v>
+        <v>1088.5</v>
       </c>
       <c r="O87" s="13" t="n">
         <v>0</v>
@@ -7014,12 +6998,12 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -7029,12 +7013,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7054,7 +7038,7 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7065,12 +7049,12 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
@@ -7086,12 +7070,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7101,12 +7085,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7126,7 +7110,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7137,16 +7121,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7158,12 +7142,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7173,7 +7157,7 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
@@ -7198,27 +7182,27 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O90" s="13" t="n">
         <v>0</v>
@@ -7230,32 +7214,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7265,32 +7249,32 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7302,32 +7286,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7337,32 +7321,32 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>204.14</v>
+        <v>140</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>0</v>
@@ -7374,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7389,11 +7373,13 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n">
-        <v/>
+          <t>CD56</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrage interface Pastell</t>
+        </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
@@ -7412,29 +7398,29 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
@@ -7444,26 +7430,28 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
@@ -7477,32 +7465,32 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>401.54</v>
+        <v>204.14</v>
       </c>
       <c r="O94" s="13" t="n">
         <v>0</v>
@@ -7514,12 +7502,12 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
@@ -7529,13 +7517,11 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v/>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
@@ -7549,34 +7535,34 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>275</v>
-      </c>
-      <c r="O95" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7586,12 +7572,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7601,13 +7587,11 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v/>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
@@ -7626,29 +7610,29 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>401.54</v>
+      </c>
+      <c r="O96" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7709,16 +7693,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>1790</v>
+        <v>275</v>
       </c>
       <c r="O97" s="13" t="n">
         <v>0</v>
@@ -7781,12 +7765,12 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
@@ -7853,18 +7837,18 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O99" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7874,12 +7858,12 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7889,11 +7873,13 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
@@ -7912,29 +7898,29 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O100" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7944,12 +7930,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7959,11 +7945,13 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E101" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
         <is>
@@ -7977,34 +7965,34 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>460</v>
-      </c>
-      <c r="O101" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="12" t="n">
@@ -8014,22 +8002,22 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E102" s="15" t="n">
@@ -8047,32 +8035,32 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>3016.08</v>
+        <v>1000</v>
       </c>
       <c r="O102" s="13" t="n">
         <v>0</v>
@@ -8084,22 +8072,22 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8122,27 +8110,27 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>1200</v>
+        <v>460</v>
       </c>
       <c r="O103" s="13" t="n">
         <v>0</v>
@@ -8154,22 +8142,22 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E104" s="15" t="n">
@@ -8187,32 +8175,32 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>3919.06</v>
+        <v>3016.08</v>
       </c>
       <c r="O104" s="13" t="n">
         <v>0</v>
@@ -8224,22 +8212,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8262,27 +8250,27 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>250</v>
+        <v>1200</v>
       </c>
       <c r="O105" s="13" t="n">
         <v>0</v>
@@ -8294,22 +8282,22 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8327,32 +8315,32 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>230</v>
+        <v>3919.06</v>
       </c>
       <c r="O106" s="13" t="n">
         <v>0</v>
@@ -8364,22 +8352,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8397,34 +8385,34 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="O107" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8434,12 +8422,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8449,7 +8437,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8467,34 +8455,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O108" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8504,12 +8492,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8519,13 +8507,11 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>SENS</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8534,27 +8520,35 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8568,12 +8562,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8583,7 +8577,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8596,7 +8590,7 @@
       </c>
       <c r="G110" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="15" t="inlineStr">
@@ -8606,17 +8600,25 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L110" s="15" t="inlineStr"/>
-      <c r="M110" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M110" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N110" s="16" t="n">
         <v>0</v>
       </c>
@@ -8630,67 +8632,61 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M111" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O111" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="12" t="n">
@@ -8700,12 +8696,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8715,7 +8711,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8728,39 +8724,31 @@
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L112" s="15" t="inlineStr"/>
+      <c r="M112" s="15" t="inlineStr"/>
       <c r="N112" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O112" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8770,22 +8758,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8793,36 +8781,44 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr"/>
-      <c r="M113" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N113" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8832,12 +8828,12 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
@@ -8847,7 +8843,7 @@
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8860,7 +8856,7 @@
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="15" t="inlineStr">
@@ -8870,21 +8866,29 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L114" s="15" t="inlineStr"/>
-      <c r="M114" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N114" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O114" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8894,12 +8898,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8909,7 +8913,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8927,30 +8931,22 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M115" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr"/>
       <c r="N115" s="12" t="n">
         <v>0</v>
       </c>
@@ -8964,12 +8960,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -8979,7 +8975,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -8992,31 +8988,27 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-25456</t>
-        </is>
-      </c>
-      <c r="M116" s="15" t="inlineStr">
-        <is>
-          <t>424152</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr"/>
+      <c r="M116" s="15" t="inlineStr"/>
       <c r="N116" s="16" t="n">
         <v>0</v>
       </c>
@@ -9030,24 +9022,26 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C117" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E117" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v/>
       </c>
       <c r="F117" s="11" t="inlineStr">
         <is>
@@ -9066,17 +9060,25 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L117" s="11" t="inlineStr"/>
-      <c r="M117" s="11" t="inlineStr"/>
+        <v>4.5</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M117" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N117" s="12" t="n">
         <v>0</v>
       </c>
@@ -9090,21 +9092,27 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v/>
+      </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9118,29 +9126,29 @@
       <c r="H118" s="15" t="inlineStr"/>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35312</t>
+          <t>PDMDEP-25456</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00177354</t>
+          <t>424152</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O118" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
@@ -9150,21 +9158,25 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr"/>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9172,20 +9184,24 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.08</v>
+        <v>0.5</v>
       </c>
       <c r="L119" s="11" t="inlineStr"/>
       <c r="M119" s="11" t="inlineStr"/>
@@ -9202,18 +9218,18 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr"/>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E120" s="15" t="inlineStr"/>
@@ -9230,29 +9246,29 @@
       <c r="H120" s="15" t="inlineStr"/>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-35312</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00177354</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O120" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9262,18 +9278,18 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr"/>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr"/>
@@ -9284,67 +9300,179 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="J121" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K121" s="11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
+      <c r="N121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr"/>
+      <c r="D122" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="inlineStr"/>
+      <c r="F122" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G122" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="inlineStr"/>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J122" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M122" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr"/>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr"/>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G123" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr"/>
+      <c r="I123" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J121" s="11" t="n">
+      <c r="J123" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K121" s="11" t="n">
+      <c r="K123" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L121" s="11" t="inlineStr">
+      <c r="L123" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M121" s="11" t="inlineStr">
+      <c r="M123" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="17" t="inlineStr">
+      <c r="N123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B122" s="17" t="inlineStr"/>
-      <c r="C122" s="17" t="inlineStr"/>
-      <c r="D122" s="17" t="inlineStr"/>
-      <c r="E122" s="17" t="inlineStr"/>
-      <c r="F122" s="17" t="inlineStr"/>
-      <c r="G122" s="17" t="inlineStr"/>
-      <c r="H122" s="17" t="inlineStr"/>
-      <c r="I122" s="17" t="inlineStr"/>
-      <c r="J122" s="17" t="inlineStr"/>
-      <c r="K122" s="17" t="inlineStr"/>
-      <c r="L122" s="17" t="inlineStr"/>
-      <c r="M122" s="17" t="inlineStr"/>
-      <c r="N122" s="18" t="n">
+      <c r="B124" s="17" t="inlineStr"/>
+      <c r="C124" s="17" t="inlineStr"/>
+      <c r="D124" s="17" t="inlineStr"/>
+      <c r="E124" s="17" t="inlineStr"/>
+      <c r="F124" s="17" t="inlineStr"/>
+      <c r="G124" s="17" t="inlineStr"/>
+      <c r="H124" s="17" t="inlineStr"/>
+      <c r="I124" s="17" t="inlineStr"/>
+      <c r="J124" s="17" t="inlineStr"/>
+      <c r="K124" s="17" t="inlineStr"/>
+      <c r="L124" s="17" t="inlineStr"/>
+      <c r="M124" s="17" t="inlineStr"/>
+      <c r="N124" s="18" t="n">
         <v>122877.162</v>
       </c>
-      <c r="O122" s="18" t="n">
+      <c r="O124" s="18" t="n">
         <v>516</v>
       </c>
-      <c r="P122" s="18" t="n">
-        <v>15.03</v>
+      <c r="P124" s="18" t="n">
+        <v>11.84</v>
       </c>
     </row>
   </sheetData>
@@ -9467,6 +9595,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9478,13 +9608,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -9504,7 +9634,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 2 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 3 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -9569,22 +9699,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -9607,37 +9737,37 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-34019</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00170492</t>
         </is>
       </c>
       <c r="K5" s="12" t="n">
-        <v>815</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -9660,12 +9790,12 @@
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31486</t>
+          <t>PDMDEP-31819</t>
         </is>
       </c>
       <c r="J6" s="15" t="inlineStr">
         <is>
-          <t>00157474</t>
+          <t>00159472</t>
         </is>
       </c>
       <c r="K6" s="16" t="n">
@@ -9673,22 +9803,75 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-31479</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE TREGUIER</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Migration vers GeoDP V2</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31486</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>00157474</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr"/>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="17" t="inlineStr"/>
-      <c r="J7" s="17" t="inlineStr"/>
-      <c r="K7" s="18" t="n">
-        <v>1630</v>
+      <c r="B8" s="17" t="inlineStr"/>
+      <c r="C8" s="17" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="17" t="inlineStr"/>
+      <c r="H8" s="17" t="inlineStr"/>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="17" t="inlineStr"/>
+      <c r="K8" s="18" t="n">
+        <v>3260</v>
       </c>
     </row>
   </sheetData>
@@ -9696,6 +9879,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10170,7 +10354,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>16</v>
+        <v>20.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>9.25</v>
@@ -10179,7 +10363,7 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>26.33</v>
+        <v>30.58</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>2.25</v>
@@ -10189,7 +10373,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -10200,16 +10384,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>0</v>
@@ -10219,7 +10403,7 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10415,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
     </row>
   </sheetData>
@@ -10319,16 +10503,16 @@
         <v>498646</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>189030</v>
+        <v>203752</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>309616</v>
+        <v>294894</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>235142</v>
+        <v>227420</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>29113</v>
+        <v>22113</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>18055</v>
@@ -10369,16 +10553,16 @@
         <v>241457</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>128479</v>
+        <v>143201</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>112978</v>
+        <v>98256</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>57828</v>
+        <v>50106</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>19938</v>
+        <v>12938</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>

--- a/jira_export_2026-10-05.xlsx
+++ b/jira_export_2026-10-05.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>60 h</t>
+          <t>61 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>285</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P124"/>
+  <dimension ref="A1:P125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1622,27 +1622,27 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35561</t>
+          <t>PDMDEP-35618</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
+          <t>[Commune de la Roche-sur-Yon] - Audit Littéralis</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
+          <t>Commune de la Roche-sur-Yon</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>API Publication</t>
+          <t>Audit Littéralis</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1662,27 +1662,27 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35567</t>
+          <t>PDMDEP-35622</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00180878</t>
+          <t>00181123</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>805.5</v>
+        <v>750</v>
       </c>
       <c r="O13" s="13" t="n">
         <v>0</v>
@@ -1694,32 +1694,32 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35469</t>
+          <t>PDMDEP-35561</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD56)] - API Publication</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VENCE</t>
+          <t>DEPARTEMENT DU MORBIHAN (CD 56)</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
+          <t>API Publication</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1729,32 +1729,32 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="J14" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35478</t>
+          <t>PDMDEP-35567</t>
         </is>
       </c>
       <c r="M14" s="15" t="inlineStr">
         <is>
-          <t>00180643</t>
+          <t>00180878</t>
         </is>
       </c>
       <c r="N14" s="16" t="n">
-        <v>4399.5</v>
+        <v>805.5</v>
       </c>
       <c r="O14" s="13" t="n">
         <v>0</v>
@@ -1766,32 +1766,32 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35460</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfert de compétence Analyse </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
@@ -1817,16 +1817,16 @@
       </c>
       <c r="L15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35464</t>
+          <t>PDMDEP-35478</t>
         </is>
       </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
-          <t>00180631</t>
+          <t>00180643</t>
         </is>
       </c>
       <c r="N15" s="12" t="n">
-        <v>455</v>
+        <v>4399.5</v>
       </c>
       <c r="O15" s="13" t="n">
         <v>0</v>
@@ -1838,12 +1838,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35445</t>
+          <t>PDMDEP-35460</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">[DEPARTEMENT DE LA CHARENTE (CD16)] - Transfert de compétence "Analyse Ref" </t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOURG EN BRESSE</t>
+          <t>DEPARTEMENT DE LA CHARENTE (CD 16)</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Mise à jour carto LIEXP SAAS</t>
+          <t xml:space="preserve">Transfert de compétence Analyse </t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H16" s="15" t="inlineStr">
@@ -1878,21 +1878,29 @@
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="J16" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L16" s="15" t="inlineStr"/>
-      <c r="M16" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35464</t>
+        </is>
+      </c>
+      <c r="M16" s="15" t="inlineStr">
+        <is>
+          <t>00180631</t>
+        </is>
+      </c>
       <c r="N16" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="16" t="n">
+        <v>455</v>
+      </c>
+      <c r="O16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="16" t="n">
@@ -1902,27 +1910,27 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35435</t>
+          <t>PDMDEP-35445</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[CD 92] - Modélisation suite audit sur site</t>
+          <t>[COMMUNE DE BOURG EN BRESSE] - Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+          <t>COMMUNE DE BOURG EN BRESSE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Modélisation suite audit sur site</t>
+          <t>Mise à jour carto LIEXP SAAS</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1932,7 +1940,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -1949,22 +1957,14 @@
         <v>1</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35439</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>00180506</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L17" s="11" t="inlineStr"/>
+      <c r="M17" s="11" t="inlineStr"/>
       <c r="N17" s="12" t="n">
-        <v>1470.38</v>
-      </c>
-      <c r="O17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P17" s="12" t="n">
@@ -1974,32 +1974,32 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35385</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ROUEN</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>GeODP - Migration V2 (presta)</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -2009,12 +2009,12 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J18" s="15" t="n">
@@ -2025,16 +2025,16 @@
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35392</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>00179700</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N18" s="16" t="n">
-        <v>5783.002</v>
+        <v>1470.38</v>
       </c>
       <c r="O18" s="13" t="n">
         <v>0</v>
@@ -2046,27 +2046,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35313</t>
+          <t>PDMDEP-35385</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
+          <t>[COMMUNE DE ROUEN] - GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAREOULT</t>
+          <t>COMMUNE DE ROUEN</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration Geodp Placier</t>
+          <t>GeODP - Migration V2 (presta)</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2086,27 +2086,27 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35319</t>
+          <t>PDMDEP-35392</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00179389</t>
+          <t>00179700</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1053</v>
+        <v>5783.002</v>
       </c>
       <c r="O19" s="13" t="n">
         <v>0</v>
@@ -2118,27 +2118,27 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35261</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
+          <t>[COMMUNE DE GAREOULT] - Migration Geodp Placier</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Reprise des données TLPE</t>
+          <t>Migration Geodp Placier</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -2158,21 +2158,29 @@
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J20" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K20" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" s="15" t="inlineStr"/>
-      <c r="M20" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35319</t>
+        </is>
+      </c>
+      <c r="M20" s="15" t="inlineStr">
+        <is>
+          <t>00179389</t>
+        </is>
+      </c>
       <c r="N20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="16" t="n">
+        <v>1053</v>
+      </c>
+      <c r="O20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P20" s="16" t="n">
@@ -2182,12 +2190,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35261</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2197,12 +2205,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>Reprise des données TLPE</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2217,34 +2225,26 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35212</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>00179038</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr"/>
       <c r="N21" s="12" t="n">
-        <v>250.5</v>
-      </c>
-      <c r="O21" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P21" s="12" t="n">
@@ -2254,12 +2254,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J22" s="15" t="n">
@@ -2305,16 +2305,16 @@
       </c>
       <c r="L22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M22" s="15" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N22" s="16" t="n">
-        <v>1465.2</v>
+        <v>250.5</v>
       </c>
       <c r="O22" s="13" t="n">
         <v>0</v>
@@ -2326,12 +2326,12 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2377,16 +2377,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>394</v>
+        <v>1465.2</v>
       </c>
       <c r="O23" s="13" t="n">
         <v>0</v>
@@ -2398,32 +2398,32 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2433,12 +2433,12 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J24" s="15" t="n">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="L24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="N24" s="16" t="n">
-        <v>1100</v>
+        <v>394</v>
       </c>
       <c r="O24" s="13" t="n">
         <v>0</v>
@@ -2470,12 +2470,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
@@ -2521,16 +2521,16 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>960</v>
+        <v>1100</v>
       </c>
       <c r="O25" s="13" t="n">
         <v>0</v>
@@ -2542,32 +2542,32 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2577,32 +2577,32 @@
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J26" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N26" s="16" t="n">
-        <v>1073.25</v>
+        <v>960</v>
       </c>
       <c r="O26" s="13" t="n">
         <v>0</v>
@@ -2614,32 +2614,32 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2665,16 +2665,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>243.6</v>
+        <v>1073.25</v>
       </c>
       <c r="O27" s="13" t="n">
         <v>0</v>
@@ -2686,32 +2686,32 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J28" s="15" t="n">
@@ -2737,16 +2737,16 @@
       </c>
       <c r="L28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M28" s="15" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N28" s="16" t="n">
-        <v>2763.25</v>
+        <v>243.6</v>
       </c>
       <c r="O28" s="13" t="n">
         <v>0</v>
@@ -2758,12 +2758,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2773,7 +2773,7 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -2805,37 +2805,37 @@
         <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>516</v>
+        <v>2763.25</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
@@ -2877,11 +2877,11 @@
         <v>3</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M30" s="15" t="inlineStr">
@@ -2890,44 +2890,44 @@
         </is>
       </c>
       <c r="N30" s="16" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O30" s="13" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>516</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2937,34 +2937,34 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P31" s="12" t="n">
@@ -2974,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
@@ -3021,22 +3021,22 @@
         <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M32" s="15" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N32" s="16" t="n">
-        <v>1620</v>
-      </c>
-      <c r="O32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="16" t="n">
@@ -3046,12 +3046,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3061,12 +3061,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3081,32 +3081,32 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>936</v>
+        <v>1620</v>
       </c>
       <c r="O33" s="13" t="n">
         <v>0</v>
@@ -3118,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J34" s="15" t="n">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M34" s="15" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N34" s="16" t="n">
-        <v>344</v>
+        <v>936</v>
       </c>
       <c r="O34" s="13" t="n">
         <v>0</v>
@@ -3190,32 +3190,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3225,32 +3225,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>153.9</v>
+        <v>344</v>
       </c>
       <c r="O35" s="13" t="n">
         <v>0</v>
@@ -3262,27 +3262,27 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
@@ -3313,16 +3313,16 @@
       </c>
       <c r="L36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M36" s="15" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N36" s="16" t="n">
-        <v>4150</v>
+        <v>153.9</v>
       </c>
       <c r="O36" s="13" t="n">
         <v>0</v>
@@ -3334,12 +3334,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3385,16 +3385,16 @@
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34310</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171605</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2500</v>
+        <v>4150</v>
       </c>
       <c r="O37" s="13" t="n">
         <v>0</v>
@@ -3406,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J38" s="15" t="n">
@@ -3457,16 +3457,16 @@
       </c>
       <c r="L38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M38" s="15" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N38" s="16" t="n">
-        <v>2649.6</v>
+        <v>2500</v>
       </c>
       <c r="O38" s="13" t="n">
         <v>0</v>
@@ -3478,32 +3478,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3529,16 +3529,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>175</v>
+        <v>2649.6</v>
       </c>
       <c r="O39" s="13" t="n">
         <v>0</v>
@@ -3550,12 +3550,12 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -3601,16 +3601,16 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M40" s="15" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N40" s="16" t="n">
-        <v>775.6</v>
+        <v>175</v>
       </c>
       <c r="O40" s="13" t="n">
         <v>0</v>
@@ -3622,27 +3622,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
@@ -3673,16 +3673,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>5388.936</v>
+        <v>775.6</v>
       </c>
       <c r="O41" s="13" t="n">
         <v>0</v>
@@ -3694,27 +3694,27 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
@@ -3745,16 +3745,16 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
       </c>
       <c r="O42" s="13" t="n">
         <v>0</v>
@@ -3766,27 +3766,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3817,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1700</v>
+        <v>177.5</v>
       </c>
       <c r="O43" s="13" t="n">
         <v>0</v>
@@ -3838,27 +3838,27 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J44" s="15" t="n">
@@ -3889,16 +3889,16 @@
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>2696</v>
+        <v>1700</v>
       </c>
       <c r="O44" s="13" t="n">
         <v>0</v>
@@ -3910,27 +3910,27 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3961,16 +3961,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>170</v>
+        <v>2696</v>
       </c>
       <c r="O45" s="13" t="n">
         <v>0</v>
@@ -3982,32 +3982,32 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
@@ -4017,32 +4017,32 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O46" s="13" t="n">
         <v>0</v>
@@ -4054,27 +4054,27 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4101,20 +4101,20 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1980</v>
+        <v>3000</v>
       </c>
       <c r="O47" s="13" t="n">
         <v>0</v>
@@ -4126,32 +4126,32 @@
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
@@ -4161,32 +4161,32 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>700</v>
+        <v>1980</v>
       </c>
       <c r="O48" s="13" t="n">
         <v>0</v>
@@ -4198,27 +4198,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O49" s="13" t="n">
         <v>0</v>
@@ -4270,32 +4270,32 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4305,32 +4305,32 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>186.235</v>
+        <v>170</v>
       </c>
       <c r="O50" s="13" t="n">
         <v>0</v>
@@ -4342,12 +4342,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4389,20 +4389,20 @@
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1890</v>
+        <v>186.235</v>
       </c>
       <c r="O51" s="13" t="n">
         <v>0</v>
@@ -4414,27 +4414,27 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
@@ -4454,27 +4454,27 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>400</v>
+        <v>1890</v>
       </c>
       <c r="O52" s="13" t="n">
         <v>0</v>
@@ -4486,12 +4486,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,27 +4526,27 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="O53" s="13" t="n">
         <v>0</v>
@@ -4558,32 +4558,32 @@
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
@@ -4598,27 +4598,27 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>203.5</v>
+        <v>552</v>
       </c>
       <c r="O54" s="13" t="n">
         <v>0</v>
@@ -4630,27 +4630,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4665,32 +4665,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O55" s="13" t="n">
         <v>0</v>
@@ -4702,27 +4702,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4753,16 +4753,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O56" s="13" t="n">
         <v>0</v>
@@ -4774,32 +4774,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O57" s="13" t="n">
         <v>0</v>
@@ -4846,27 +4846,27 @@
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
@@ -4897,16 +4897,16 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>400</v>
+        <v>171.4</v>
       </c>
       <c r="O58" s="13" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4969,16 +4969,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>6177.52</v>
+        <v>400</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>0</v>
@@ -4990,27 +4990,27 @@
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -5041,16 +5041,16 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>500</v>
+        <v>6177.52</v>
       </c>
       <c r="O60" s="13" t="n">
         <v>0</v>
@@ -5062,37 +5062,37 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -5102,21 +5102,29 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L61" s="11" t="inlineStr"/>
-      <c r="M61" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33401</t>
+        </is>
+      </c>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>00167624</t>
+        </is>
+      </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O61" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5126,37 +5134,37 @@
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H62" s="15" t="inlineStr">
@@ -5166,29 +5174,21 @@
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M62" s="15" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L62" s="15" t="inlineStr"/>
+      <c r="M62" s="15" t="inlineStr"/>
       <c r="N62" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O62" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="16" t="n">
@@ -5198,27 +5198,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5249,16 +5249,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>0</v>
@@ -5270,32 +5270,32 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J64" s="15" t="n">
@@ -5321,16 +5321,16 @@
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O64" s="13" t="n">
         <v>0</v>
@@ -5393,16 +5393,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O65" s="13" t="n">
         <v>0</v>
@@ -5414,32 +5414,32 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
@@ -5465,16 +5465,16 @@
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
-        <v>1047</v>
+        <v>320</v>
       </c>
       <c r="O66" s="13" t="n">
         <v>0</v>
@@ -5486,32 +5486,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5521,32 +5521,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>400</v>
+        <v>1047</v>
       </c>
       <c r="O67" s="13" t="n">
         <v>0</v>
@@ -5558,32 +5558,32 @@
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
@@ -5609,16 +5609,16 @@
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N68" s="16" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O68" s="13" t="n">
         <v>0</v>
@@ -5630,12 +5630,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
@@ -5681,16 +5681,16 @@
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>680.8</v>
+        <v>200</v>
       </c>
       <c r="O69" s="13" t="n">
         <v>0</v>
@@ -5702,12 +5702,12 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -5737,12 +5737,12 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
@@ -5753,16 +5753,16 @@
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O70" s="13" t="n">
         <v>0</v>
@@ -5774,32 +5774,32 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
@@ -5825,16 +5825,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O71" s="13" t="n">
         <v>0</v>
@@ -5846,32 +5846,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
@@ -5897,16 +5897,16 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>276</v>
+        <v>403.074</v>
       </c>
       <c r="O72" s="13" t="n">
         <v>0</v>
@@ -5918,32 +5918,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5969,16 +5969,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>142.1</v>
+        <v>276</v>
       </c>
       <c r="O73" s="13" t="n">
         <v>0</v>
@@ -5990,32 +5990,32 @@
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6025,32 +6025,32 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J74" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K74" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O74" s="13" t="n">
         <v>0</v>
@@ -6062,32 +6062,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6097,12 +6097,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6113,16 +6113,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O75" s="13" t="n">
         <v>0</v>
@@ -6134,32 +6134,32 @@
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
@@ -6185,16 +6185,16 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O76" s="13" t="n">
         <v>0</v>
@@ -6206,12 +6206,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6257,16 +6257,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O77" s="13" t="n">
         <v>0</v>
@@ -6278,32 +6278,32 @@
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O78" s="13" t="n">
         <v>0</v>
@@ -6350,32 +6350,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6385,32 +6385,32 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O79" s="13" t="n">
         <v>0</v>
@@ -6422,27 +6422,27 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
@@ -6473,16 +6473,16 @@
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>1050</v>
+        <v>3240</v>
       </c>
       <c r="O80" s="13" t="n">
         <v>0</v>
@@ -6494,27 +6494,27 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6545,16 +6545,16 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O81" s="13" t="n">
         <v>0</v>
@@ -6566,32 +6566,32 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
@@ -6601,34 +6601,34 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="16" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O82" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P82" s="16" t="n">
@@ -6638,32 +6638,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6673,34 +6673,34 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="12" t="n">
@@ -6710,32 +6710,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
@@ -6761,16 +6761,16 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O84" s="13" t="n">
         <v>0</v>
@@ -6782,32 +6782,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
@@ -6833,16 +6833,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O85" s="13" t="n">
         <v>0</v>
@@ -6854,27 +6854,27 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6889,32 +6889,32 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K86" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O86" s="13" t="n">
         <v>0</v>
@@ -6926,32 +6926,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6977,16 +6977,16 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O87" s="13" t="n">
         <v>0</v>
@@ -6998,32 +6998,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7049,16 +7049,16 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O88" s="13" t="n">
         <v>0</v>
@@ -7070,12 +7070,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7121,16 +7121,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O89" s="13" t="n">
         <v>0</v>
@@ -7142,12 +7142,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
@@ -7193,16 +7193,16 @@
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O90" s="13" t="n">
         <v>0</v>
@@ -7214,12 +7214,12 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
@@ -7265,16 +7265,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O91" s="13" t="n">
         <v>0</v>
@@ -7286,12 +7286,12 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7326,27 +7326,27 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>0</v>
@@ -7358,32 +7358,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7393,32 +7393,32 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O93" s="13" t="n">
         <v>0</v>
@@ -7430,27 +7430,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7470,27 +7470,27 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>204.14</v>
+        <v>230</v>
       </c>
       <c r="O94" s="13" t="n">
         <v>0</v>
@@ -7502,26 +7502,28 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E95" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
         <is>
@@ -7540,29 +7542,29 @@
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="12" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="12" t="n">
@@ -7572,12 +7574,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7587,7 +7589,7 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E96" s="15" t="n">
@@ -7605,34 +7607,34 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O96" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7642,12 +7644,12 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
@@ -7657,13 +7659,11 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7682,27 +7682,27 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O97" s="13" t="n">
         <v>0</v>
@@ -7765,18 +7765,18 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>275</v>
+      </c>
+      <c r="O98" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7837,18 +7837,18 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7909,18 +7909,18 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="16" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O100" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -8002,12 +8002,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8017,11 +8017,13 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -8040,29 +8042,29 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O102" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8072,12 +8074,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8087,7 +8089,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8105,12 +8107,12 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
@@ -8121,16 +8123,16 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O103" s="13" t="n">
         <v>0</v>
@@ -8142,22 +8144,22 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E104" s="15" t="n">
@@ -8180,27 +8182,27 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>3016.08</v>
+        <v>460</v>
       </c>
       <c r="O104" s="13" t="n">
         <v>0</v>
@@ -8212,12 +8214,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8227,7 +8229,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8250,27 +8252,27 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O105" s="13" t="n">
         <v>0</v>
@@ -8282,22 +8284,22 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8315,32 +8317,32 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O106" s="13" t="n">
         <v>0</v>
@@ -8352,12 +8354,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8367,7 +8369,7 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8385,32 +8387,32 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>250</v>
+        <v>3919.06</v>
       </c>
       <c r="O107" s="13" t="n">
         <v>0</v>
@@ -8422,22 +8424,22 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8460,27 +8462,27 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>18</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O108" s="13" t="n">
         <v>0</v>
@@ -8492,12 +8494,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8507,7 +8509,7 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8525,34 +8527,34 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8562,12 +8564,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8577,7 +8579,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8600,23 +8602,23 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
@@ -8632,12 +8634,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8647,13 +8649,11 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -8662,27 +8662,35 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K111" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L111" s="11" t="inlineStr"/>
-      <c r="M111" s="11" t="inlineStr"/>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8696,12 +8704,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8711,11 +8719,13 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8729,19 +8739,19 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr"/>
       <c r="M112" s="15" t="inlineStr"/>
@@ -8758,22 +8768,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8781,44 +8791,36 @@
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M113" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
       <c r="N113" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O113" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="12" t="n">
@@ -8828,22 +8830,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8851,7 +8853,7 @@
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G114" s="15" t="inlineStr">
@@ -8861,12 +8863,12 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
@@ -8877,16 +8879,16 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O114" s="13" t="n">
         <v>0</v>
@@ -8898,22 +8900,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8926,7 +8928,7 @@
       </c>
       <c r="G115" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -8936,21 +8938,29 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L115" s="11" t="inlineStr"/>
-      <c r="M115" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L115" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="12" t="n">
@@ -8960,22 +8970,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -8998,14 +9008,14 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L116" s="15" t="inlineStr"/>
       <c r="M116" s="15" t="inlineStr"/>
@@ -9022,22 +9032,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9055,30 +9065,22 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L117" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M117" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L117" s="11" t="inlineStr"/>
+      <c r="M117" s="11" t="inlineStr"/>
       <c r="N117" s="12" t="n">
         <v>0</v>
       </c>
@@ -9092,22 +9094,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9120,29 +9122,33 @@
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H118" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.75</v>
+        <v>4.5</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9158,24 +9164,26 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C119" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C119" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E119" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v/>
       </c>
       <c r="F119" s="11" t="inlineStr">
         <is>
@@ -9184,27 +9192,31 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr"/>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9218,21 +9230,25 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr"/>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9240,35 +9256,31 @@
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M120" s="15" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr"/>
+      <c r="M120" s="15" t="inlineStr"/>
       <c r="N120" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O120" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9278,18 +9290,18 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr"/>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr"/>
@@ -9300,27 +9312,35 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr"/>
-      <c r="M121" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9330,18 +9350,18 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr"/>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E122" s="15" t="inlineStr"/>
@@ -9352,31 +9372,23 @@
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr"/>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
@@ -9390,18 +9402,18 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr"/>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
@@ -9418,61 +9430,121 @@
       <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J123" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr"/>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="inlineStr"/>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="inlineStr"/>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J123" s="11" t="n">
+      <c r="J124" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="K123" s="11" t="n">
+      <c r="K124" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L123" s="11" t="inlineStr">
+      <c r="L124" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M123" s="11" t="inlineStr">
+      <c r="M124" s="15" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="17" t="inlineStr">
+      <c r="N124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B124" s="17" t="inlineStr"/>
-      <c r="C124" s="17" t="inlineStr"/>
-      <c r="D124" s="17" t="inlineStr"/>
-      <c r="E124" s="17" t="inlineStr"/>
-      <c r="F124" s="17" t="inlineStr"/>
-      <c r="G124" s="17" t="inlineStr"/>
-      <c r="H124" s="17" t="inlineStr"/>
-      <c r="I124" s="17" t="inlineStr"/>
-      <c r="J124" s="17" t="inlineStr"/>
-      <c r="K124" s="17" t="inlineStr"/>
-      <c r="L124" s="17" t="inlineStr"/>
-      <c r="M124" s="17" t="inlineStr"/>
-      <c r="N124" s="18" t="n">
-        <v>122877.162</v>
-      </c>
-      <c r="O124" s="18" t="n">
+      <c r="B125" s="17" t="inlineStr"/>
+      <c r="C125" s="17" t="inlineStr"/>
+      <c r="D125" s="17" t="inlineStr"/>
+      <c r="E125" s="17" t="inlineStr"/>
+      <c r="F125" s="17" t="inlineStr"/>
+      <c r="G125" s="17" t="inlineStr"/>
+      <c r="H125" s="17" t="inlineStr"/>
+      <c r="I125" s="17" t="inlineStr"/>
+      <c r="J125" s="17" t="inlineStr"/>
+      <c r="K125" s="17" t="inlineStr"/>
+      <c r="L125" s="17" t="inlineStr"/>
+      <c r="M125" s="17" t="inlineStr"/>
+      <c r="N125" s="18" t="n">
+        <v>123627.162</v>
+      </c>
+      <c r="O125" s="18" t="n">
         <v>516</v>
       </c>
-      <c r="P124" s="18" t="n">
-        <v>11.84</v>
+      <c r="P125" s="18" t="n">
+        <v>11.64</v>
       </c>
     </row>
   </sheetData>
@@ -9597,6 +9669,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10354,7 +10427,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>20.25</v>
+        <v>21</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>9.25</v>
@@ -10363,7 +10436,7 @@
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>30.58</v>
+        <v>31.33</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>2.25</v>
@@ -10373,7 +10446,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10488,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
     </row>
   </sheetData>
@@ -10579,7 +10652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10603,7 +10676,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 1 commande(s)</t>
+          <t>Épics créées ce mois — 2 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10658,73 +10731,97 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-36181</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-36174</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE AURAY</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>00183814</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I5" s="25" t="n">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n"/>
-      <c r="C6" s="17" t="n"/>
-      <c r="D6" s="17" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="F6" s="17" t="n"/>
-      <c r="G6" s="17" t="n"/>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t>1 commande(s)</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="26" t="n">
         <v>2310</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B7" s="17" t="n"/>
@@ -10735,7 +10832,7 @@
       <c r="G7" s="17" t="n"/>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>2 commande(s)</t>
         </is>
       </c>
       <c r="I7" s="24" t="n">
@@ -10745,7 +10842,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -10756,10 +10853,31 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>0 commande(s)</t>
+          <t>1 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="inlineStr">
+        <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-10-05.xlsx
+++ b/jira_export_2026-10-05.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>516 €</t>
+          <t>1,243 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>0 €</t>
+          <t>727 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>61 h</t>
+          <t>81 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P125"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3021,7 +3021,7 @@
         <v>3</v>
       </c>
       <c r="K32" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L32" s="15" t="inlineStr">
         <is>
@@ -4189,10 +4189,10 @@
         <v>1980</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="49">
@@ -4533,7 +4533,7 @@
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>4</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>12</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
@@ -8275,10 +8275,10 @@
         <v>3016.08</v>
       </c>
       <c r="O105" s="13" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P105" s="12" t="n">
-        <v>0</v>
+        <v>69.81999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -8424,12 +8424,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8457,34 +8457,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K108" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O108" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8494,22 +8494,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8532,27 +8532,27 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>18</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O109" s="13" t="n">
         <v>0</v>
@@ -8564,12 +8564,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8597,34 +8597,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O110" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8634,12 +8634,12 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8672,23 +8672,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8704,12 +8704,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8719,13 +8719,11 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8734,27 +8732,35 @@
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K112" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="L112" s="15" t="inlineStr"/>
-      <c r="M112" s="15" t="inlineStr"/>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
@@ -8768,12 +8774,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8783,11 +8789,13 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F113" s="11" t="inlineStr">
         <is>
@@ -8801,19 +8809,19 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr"/>
       <c r="M113" s="11" t="inlineStr"/>
@@ -8830,22 +8838,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8853,44 +8861,36 @@
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M114" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr"/>
+      <c r="M114" s="15" t="inlineStr"/>
       <c r="N114" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O114" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8900,22 +8900,22 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8923,7 +8923,7 @@
       </c>
       <c r="F115" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G115" s="11" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H115" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
@@ -8949,16 +8949,16 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O115" s="13" t="n">
         <v>0</v>
@@ -8970,22 +8970,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
@@ -9008,21 +9008,29 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L116" s="15" t="inlineStr"/>
-      <c r="M116" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L116" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M116" s="15" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O116" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9032,22 +9040,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9070,14 +9078,14 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L117" s="11" t="inlineStr"/>
       <c r="M117" s="11" t="inlineStr"/>
@@ -9094,22 +9102,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9127,30 +9135,22 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L118" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L118" s="15" t="inlineStr"/>
+      <c r="M118" s="15" t="inlineStr"/>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
@@ -9164,22 +9164,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9192,29 +9192,33 @@
       </c>
       <c r="G119" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.75</v>
+        <v>5</v>
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9230,24 +9234,26 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v/>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
@@ -9256,27 +9262,31 @@
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H120" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr"/>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>37</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr"/>
-      <c r="M120" s="15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N120" s="16" t="n">
         <v>0</v>
       </c>
@@ -9290,21 +9300,25 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr"/>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
-        </is>
-      </c>
-      <c r="E121" s="11" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F121" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9312,35 +9326,31 @@
       </c>
       <c r="G121" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H121" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M121" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
       <c r="N121" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9350,18 +9360,18 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr"/>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E122" s="15" t="inlineStr"/>
@@ -9372,27 +9382,35 @@
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr"/>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr"/>
-      <c r="M122" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M122" s="15" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N122" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>450</v>
+      </c>
+      <c r="O122" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9402,18 +9420,18 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr"/>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr"/>
@@ -9424,31 +9442,23 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M123" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9462,18 +9472,18 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr"/>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E124" s="15" t="inlineStr"/>
@@ -9490,61 +9500,121 @@
       <c r="H124" s="15" t="inlineStr"/>
       <c r="I124" s="15" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J124" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K124" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr"/>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr"/>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr"/>
+      <c r="I125" s="11" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J124" s="15" t="n">
+      <c r="J125" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="K124" s="15" t="n">
+      <c r="K125" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L124" s="15" t="inlineStr">
+      <c r="L125" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M124" s="15" t="inlineStr">
+      <c r="M125" s="11" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N124" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="17" t="inlineStr">
+      <c r="N125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B125" s="17" t="inlineStr"/>
-      <c r="C125" s="17" t="inlineStr"/>
-      <c r="D125" s="17" t="inlineStr"/>
-      <c r="E125" s="17" t="inlineStr"/>
-      <c r="F125" s="17" t="inlineStr"/>
-      <c r="G125" s="17" t="inlineStr"/>
-      <c r="H125" s="17" t="inlineStr"/>
-      <c r="I125" s="17" t="inlineStr"/>
-      <c r="J125" s="17" t="inlineStr"/>
-      <c r="K125" s="17" t="inlineStr"/>
-      <c r="L125" s="17" t="inlineStr"/>
-      <c r="M125" s="17" t="inlineStr"/>
-      <c r="N125" s="18" t="n">
+      <c r="B126" s="17" t="inlineStr"/>
+      <c r="C126" s="17" t="inlineStr"/>
+      <c r="D126" s="17" t="inlineStr"/>
+      <c r="E126" s="17" t="inlineStr"/>
+      <c r="F126" s="17" t="inlineStr"/>
+      <c r="G126" s="17" t="inlineStr"/>
+      <c r="H126" s="17" t="inlineStr"/>
+      <c r="I126" s="17" t="inlineStr"/>
+      <c r="J126" s="17" t="inlineStr"/>
+      <c r="K126" s="17" t="inlineStr"/>
+      <c r="L126" s="17" t="inlineStr"/>
+      <c r="M126" s="17" t="inlineStr"/>
+      <c r="N126" s="18" t="n">
         <v>123627.162</v>
       </c>
-      <c r="O125" s="18" t="n">
-        <v>516</v>
-      </c>
-      <c r="P125" s="18" t="n">
-        <v>11.64</v>
+      <c r="O126" s="18" t="n">
+        <v>1242.9</v>
+      </c>
+      <c r="P126" s="18" t="n">
+        <v>24.82</v>
       </c>
     </row>
   </sheetData>
@@ -9670,6 +9740,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10427,26 +10498,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>21</v>
+        <v>26.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>1.08</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>31.33</v>
+        <v>37.08</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>2.25</v>
+        <v>5.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>508.2</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
@@ -10488,7 +10559,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>13.25</v>
+        <v>24.25</v>
       </c>
     </row>
   </sheetData>
@@ -10573,16 +10644,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>498646</v>
+        <v>497919</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>203752</v>
+        <v>203444</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>294894</v>
+        <v>294475</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>227420</v>
+        <v>227001</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>22113</v>
@@ -10598,16 +10669,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>257189</v>
+        <v>256462</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>60551</v>
+        <v>60243</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>196638</v>
+        <v>196219</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>177313</v>
+        <v>176894</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>9175</v>
@@ -10652,7 +10723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10676,7 +10747,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 2 commande(s)</t>
+          <t>Épics créées ce mois — 3 commande(s)</t>
         </is>
       </c>
     </row>
@@ -10776,73 +10847,97 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-36197</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-36190</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BAUGE-EN-ANJOU</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>00183894</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-36148</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-36144</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>01/10/2026</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>VILLE DE VILLEFRANCHE SUR SAONE</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>00183228</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
-        <v>2310</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="25" t="n">
         <v>2310</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -10853,7 +10948,7 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>3 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
@@ -10863,7 +10958,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B9" s="17" t="n"/>
@@ -10874,10 +10969,31 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="inlineStr">
         <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
           <t>1 commande(s)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
